--- a/docs/CIEL1/CCF/CCF_2025/grille_comp_CCF.xlsx
+++ b/docs/CIEL1/CCF/CCF_2025/grille_comp_CCF.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\--- LYCEE ---\ENSEIGNEMENT_G\docs\CIEL1\CCF\CCF_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7C61D4-F654-4728-91CD-8EBEECA766C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5118CAF-B7A3-4284-80A9-4B84F2DD94C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5323A597-3EF7-45E9-BE64-C65DC6E6C1EB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{5323A597-3EF7-45E9-BE64-C65DC6E6C1EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -383,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -440,7 +441,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,7 +756,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F774E324-096C-456C-BFF9-9E511558E414}">
   <dimension ref="A1:BO34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="6.53125" defaultRowHeight="17.75" customHeight="1" thickBottom="1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.53125" defaultRowHeight="13.25" customHeight="1" thickBottom="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="3" max="3" width="6.53125" style="3"/>
     <col min="4" max="4" width="15.1328125" style="3" customWidth="1"/>
@@ -796,7 +796,7 @@
     <col min="67" max="67" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="17.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:67" ht="13.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B1" t="s">
         <v>29</v>
       </c>
@@ -868,7 +868,7 @@
       <c r="AG1" s="31"/>
       <c r="AI1" s="15"/>
     </row>
-    <row r="2" spans="1:67" s="1" customFormat="1" ht="17.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:67" s="1" customFormat="1" ht="13.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
@@ -955,7 +955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:67" ht="17.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D3" s="11"/>
       <c r="E3" s="21" t="s">
         <v>20</v>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="AQ3" s="1"/>
     </row>
-    <row r="4" spans="1:67" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:67" ht="13.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6">
         <f>A5+1</f>
         <v>2</v>
@@ -1603,7 +1603,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7">
         <f t="shared" ref="A7:A32" si="31">A6+1</f>
         <v>3</v>
@@ -1808,7 +1808,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="8" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8">
         <f t="shared" si="31"/>
         <v>4</v>
@@ -2013,7 +2013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9">
         <f t="shared" si="31"/>
         <v>5</v>
@@ -2218,7 +2218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10">
         <f t="shared" si="31"/>
         <v>6</v>
@@ -2423,7 +2423,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="11" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11">
         <f t="shared" si="31"/>
         <v>7</v>
@@ -2628,7 +2628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12">
         <f t="shared" si="31"/>
         <v>8</v>
@@ -2833,7 +2833,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <f t="shared" si="31"/>
         <v>9</v>
@@ -3038,7 +3038,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="14" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14">
         <f t="shared" si="31"/>
         <v>10</v>
@@ -3243,7 +3243,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15">
         <f t="shared" si="31"/>
         <v>11</v>
@@ -3448,7 +3448,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16">
         <f t="shared" si="31"/>
         <v>12</v>
@@ -3653,7 +3653,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="17.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17">
         <f t="shared" si="31"/>
         <v>13</v>
@@ -3858,7 +3858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:67" ht="17.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18">
         <f t="shared" si="31"/>
         <v>14</v>
@@ -4063,7 +4063,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="19" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19">
         <f t="shared" si="31"/>
         <v>15</v>
@@ -4268,7 +4268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20">
         <f t="shared" si="31"/>
         <v>16</v>
@@ -4473,7 +4473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21">
         <f t="shared" si="31"/>
         <v>17</v>
@@ -4676,7 +4676,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22">
         <f t="shared" si="31"/>
         <v>18</v>
@@ -4881,7 +4881,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="23" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23">
         <f t="shared" si="31"/>
         <v>19</v>
@@ -5086,7 +5086,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="24" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24">
         <f t="shared" si="31"/>
         <v>20</v>
@@ -5291,7 +5291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>59</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="26" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26">
         <f>A24+1</f>
         <v>21</v>
@@ -5697,7 +5697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27">
         <f t="shared" si="31"/>
         <v>22</v>
@@ -5902,7 +5902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:67" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28">
         <f t="shared" si="31"/>
         <v>23</v>
@@ -6107,7 +6107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:67" ht="13.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29">
         <f t="shared" si="31"/>
         <v>24</v>
@@ -6312,7 +6312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:67" ht="13.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30">
         <f t="shared" si="31"/>
         <v>25</v>
@@ -6517,7 +6517,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="31" spans="1:67" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31">
         <f t="shared" si="31"/>
         <v>26</v>
@@ -6721,7 +6721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:67" ht="17.649999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32">
         <f t="shared" si="31"/>
         <v>27</v>
@@ -6786,7 +6786,7 @@
       <c r="W32" s="24">
         <v>2</v>
       </c>
-      <c r="X32" s="42">
+      <c r="X32">
         <v>2</v>
       </c>
       <c r="Y32" s="28">
@@ -6926,7 +6926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="5:67" ht="17.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="5:67" ht="13.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E33" s="7"/>
       <c r="F33" s="35"/>
       <c r="G33" s="24"/>
@@ -6959,11 +6959,11 @@
       <c r="AH33" s="28"/>
       <c r="AI33"/>
       <c r="BO33">
-        <f t="shared" ref="BO33" si="32">BO32/2</f>
-        <v>4.5</v>
+        <f>AVERAGE(BO6:BO32)</f>
+        <v>5.5925925925925926</v>
       </c>
     </row>
-    <row r="34" spans="5:67" ht="17.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="5:67" ht="13.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="E34" s="7"/>
       <c r="F34" s="35"/>
       <c r="G34" s="24"/>
@@ -6996,8 +6996,8 @@
       <c r="AH34" s="28"/>
       <c r="AI34"/>
       <c r="BO34">
-        <f t="shared" ref="BO34" si="33">BO33*100</f>
-        <v>450</v>
+        <f t="shared" ref="BO34" si="32">BO33*100</f>
+        <v>559.25925925925924</v>
       </c>
     </row>
   </sheetData>
@@ -7005,4 +7005,297 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCAFC26-A076-4CD2-810F-4F4A63BEC89F}">
+  <dimension ref="A2:B30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="28.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="str">
+        <f>Feuil1!B5</f>
+        <v>ACCAR Roger</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="str">
+        <f>Feuil1!B6</f>
+        <v>ADO Oihan</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="str">
+        <f>Feuil1!B7</f>
+        <v>ALAUZET Mathis</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="str">
+        <f>Feuil1!B8</f>
+        <v>ARSLANE Djibril</v>
+      </c>
+      <c r="B5">
+        <f>Feuil1!BO8</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="str">
+        <f>Feuil1!B9</f>
+        <v>BENGOUA Solaymane</v>
+      </c>
+      <c r="B6">
+        <f>Feuil1!BO9</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="str">
+        <f>Feuil1!B10</f>
+        <v>BILINGBI MAX Pierre Bradley</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="str">
+        <f>Feuil1!B11</f>
+        <v>BONVALET icolas</v>
+      </c>
+      <c r="B8">
+        <f>Feuil1!BO11</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="str">
+        <f>Feuil1!B12</f>
+        <v>BRENEK Ethan</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="str">
+        <f>Feuil1!B13</f>
+        <v>CHABAUD Nathaniel</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="str">
+        <f>Feuil1!B14</f>
+        <v>COMBES Sinclair</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="str">
+        <f>Feuil1!B15</f>
+        <v>EL BOUKHARI Khayfallah</v>
+      </c>
+      <c r="B12">
+        <f>Feuil1!BO15</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="str">
+        <f>Feuil1!B16</f>
+        <v>ELEB Mark</v>
+      </c>
+      <c r="B13">
+        <f>Feuil1!BO16</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="str">
+        <f>Feuil1!B17</f>
+        <v>FACCINI Adrien</v>
+      </c>
+      <c r="B14">
+        <f>Feuil1!BO17</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="str">
+        <f>Feuil1!B18</f>
+        <v>FOURCADE Piere</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="str">
+        <f>Feuil1!B19</f>
+        <v>GIROUD Quentin</v>
+      </c>
+      <c r="B16">
+        <f>Feuil1!BO19</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="str">
+        <f>Feuil1!B20</f>
+        <v>JABELKHAYR Hatim</v>
+      </c>
+      <c r="B17">
+        <f>Feuil1!BO20</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="str">
+        <f>Feuil1!B21</f>
+        <v>JOUE--CREITER Lukas</v>
+      </c>
+      <c r="B18">
+        <f>Feuil1!BO21</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="str">
+        <f>Feuil1!B22</f>
+        <v>JUDE Stephan</v>
+      </c>
+      <c r="B19">
+        <f>Feuil1!BO22</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="str">
+        <f>Feuil1!B23</f>
+        <v>KADRI Elias</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="str">
+        <f>Feuil1!B24</f>
+        <v>KHADIRI Abd el Ali</v>
+      </c>
+      <c r="B21">
+        <f>Feuil1!BO24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="str">
+        <f>Feuil1!B25</f>
+        <v>MAZABRAUD</v>
+      </c>
+      <c r="B22">
+        <f>Feuil1!BO25</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="str">
+        <f>Feuil1!B26</f>
+        <v>MORAGLIA Lowan</v>
+      </c>
+      <c r="B23">
+        <f>Feuil1!BO26</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="str">
+        <f>Feuil1!B27</f>
+        <v>MOREAU Jean</v>
+      </c>
+      <c r="B24">
+        <f>Feuil1!BO27</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="str">
+        <f>Feuil1!B28</f>
+        <v>NGUEDAM Kiara</v>
+      </c>
+      <c r="B25">
+        <f>Feuil1!BO28</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="str">
+        <f>Feuil1!B29</f>
+        <v>RIBEIRO Diala</v>
+      </c>
+      <c r="B26">
+        <f>Feuil1!BO29</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="str">
+        <f>Feuil1!B30</f>
+        <v>RODRIGUES Leandro</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="str">
+        <f>Feuil1!B31</f>
+        <v>SEGUY Axel</v>
+      </c>
+      <c r="B28">
+        <f>Feuil1!BO31</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="str">
+        <f>Feuil1!B32</f>
+        <v>TRESMONTAN Jordan</v>
+      </c>
+      <c r="B29">
+        <f>Feuil1!BO32</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <f>Feuil1!B33</f>
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <f>AVERAGE(B2:B29)</f>
+        <v>5.6607142857142856</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>